--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-dev</t>
+    <t>1.2.0a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0a</t>
+    <t>1.2.0-a-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-a</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-a-dev</t>
+    <t>1.2.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -278,7 +278,7 @@
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が必要です / A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>Event</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-release</t>
+    <t>1.2.0-b</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2071" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2072" uniqueCount="399">
   <si>
     <t>Property</t>
   </si>
@@ -269,12 +269,12 @@
     <t>診断レポート-依頼情報、１項目単位の結果、画像、解釈、およびフォーマットされたレポートの組み合わせ　【JP Core仕様】口腔診査結果レポートのプロフィール</t>
   </si>
   <si>
-    <t>患者、患者のグループ、デバイス、場所、これらから派生した対象に対して実行された診断的検査の結果と解釈。レポートには、依頼情報や依頼者情報などの臨床コンテキスト（文脈）、および１項目単位の結果、画像、テキストとコード化された解釈、および診断レポートのフォーマットされた表現のいくつかの組み合わせが含まれる。
-【JP Core仕様】口腔診査結果レポートのプロフィール</t>
-  </si>
-  <si>
-    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
-【JP Core仕様】DiagnosticReportリソースの共通プロフィール</t>
+    <t>患者、患者のグループ、デバイス、場所、これらから派生した対象に対して実行された診断的検査の結果と解釈。レポートには、依頼情報や依頼者情報などの臨床コンテキスト（文脈）、および１項目単位の結果、画像、テキストとコード化された解釈、および診断レポートのフォーマットされた表現のいくつかの組み合わせが含まれる。
+【JP Core仕様】口腔診査結果レポートのプロファイル</t>
+  </si>
+  <si>
+    <t>これは単一のレポートをキャプチャすることを目的としており、複数のレポートをカバーする要約情報の表示に使用するのには適していない。たとえば、このリソースは、検査結果の累積レポート形式やシーケンスの詳細な構造化レポート用に作られていない。
+【JP Core仕様】DiagnosticReportリソースの共通プロファイル</t>
   </si>
   <si>
     <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
@@ -489,10 +489,11 @@
 </t>
   </si>
   <si>
-    <t>当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
-  </si>
-  <si>
-    <t>通常、診断サービスプロバイダの情報システム（フィラーID）によって割り当てられる。</t>
+    <t>レポートを識別するビジネス識別子  
+【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
+  </si>
+  <si>
+    <t>例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
   </si>
   <si>
     <t>発生源の検査室からこのレポートについてクエリを作成するとき、およびFHIRコンテキスト外のレポートにリンクするときに使用する識別子を知る必要がある。</t>
@@ -521,7 +522,8 @@
 </t>
   </si>
   <si>
-    <t>オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
+    <t>元になった検査や診断の依頼  
+【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
   </si>
   <si>
     <t>通常、１結果ごとに１つの検査依頼があるが、状況によっては、複数の検査要求に対して１レポートがある場合がある。また１つの検査依頼に対して複数のレポートが作成される場合もあることに注意。</t>
@@ -542,7 +544,8 @@
     <t>DiagnosticReport.status</t>
   </si>
   <si>
-    <t>診断レポートのステータス。レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
+    <t>診断レポートのステータス  
+【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
   </si>
   <si>
     <t>診断サービスは、暫定/不完全なレポートを日常的に発行し、以前にリリースされたレポートを撤回することもあります。 / Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
@@ -909,7 +912,8 @@
 </t>
   </si>
   <si>
-    <t>Paitientリソースを参照</t>
+    <t>レポートの対象、常にではないが、通常は患者  
+【JP Core仕様】Patientリソースを参照</t>
   </si>
   <si>
     <t>レポートの対象、通常、Patientリソースへの参照。ただし、他のさまざまなソースから収集された検体を対象とすることもある。参照は内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
@@ -941,10 +945,11 @@
 </t>
   </si>
   <si>
-    <t>このレポートを書く切っ掛けとなるEncounterリソースを参照。例：診療、歯科健診（検診）、身元不明者調査</t>
-  </si>
-  <si>
-    <t>受診、入院、診察など。通常、イベントが発生したEncounterであるが、一部のイベントは、Encounterの正式な完了の前または後に開始される場合があり、その場合でもEncounterのコンテキストに関連付けられている（例：入院前の臨床検査）。</t>
+    <t>依頼時におけるヘルスケアイベント（受診など）  
+【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+  </si>
+  <si>
+    <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>
   </si>
   <si>
     <t>リクエストをエンカウンターコンテキストにリンクします。 / Links the request to the Encounter context.</t>
@@ -973,7 +978,8 @@
 </t>
   </si>
   <si>
-    <t>レポート作成日時</t>
+    <t>臨床的に関連する時刻または時間  
+【JP Core仕様】レポート作成日時</t>
   </si>
   <si>
     <t>観測値が関連する時間または期間。レポートの対象が患者である場合、これは通常、読影開始の時間であり、日付／時刻自体のみ提供される。実施日時。</t>
@@ -1005,7 +1011,8 @@
 </t>
   </si>
   <si>
-    <t>最新のレポート確定日時</t>
+    <t>このバージョンが作成された日時  
+【JP Core仕様】最新のレポート確定日時</t>
   </si>
   <si>
     <t>通常、レポートがレビューおよび検証・確定された後となる。リソース自体の更新時刻とは異なる場合がある。これは、レポートの実際の提供時刻ではなく、リソース自体の更新時刻はレコード（場合によってはセカンダリコピー）のステータスの更新時刻となるため。</t>
@@ -1034,10 +1041,11 @@
 </t>
   </si>
   <si>
-    <t>レポート確定者。例：歯科医師など</t>
-  </si>
-  <si>
-    <t>必ずしも１項目データ単位のデータソースまたは結果を解釈した主体でなない。臨床レポートに責任をもつ主体のこと。</t>
+    <t>レポート内容に責任をもつ診断的サービス  
+【JP Core仕様】レポート確定者</t>
+  </si>
+  <si>
+    <t>例：歯科医師など</t>
   </si>
   <si>
     <t>結果についてクエリがある場合は、誰に連絡するかを知る必要があります。また、二次データ分析のためにレポートのソースを追跡する必要がある場合があります。 / Need to know whom to contact if there are queries about the results. Also may need to track the source of reports for secondary data analysis.</t>
@@ -1062,10 +1070,11 @@
 Reported by</t>
   </si>
   <si>
-    <t>レポートの作成者。例：歯科医師、歯科研修医など</t>
-  </si>
-  <si>
-    <t>診断レポートに責任を持つもの(performer)とは異なる場合がある。</t>
+    <t>結果の一次解釈者  
+【JP Core仕様】レポートの作成者</t>
+  </si>
+  <si>
+    <t>例：歯科医師、歯科研修医など</t>
   </si>
   <si>
     <t>OBR-32, PRT-8 (where this PRT-4-Participation = "PI")</t>
@@ -1078,7 +1087,8 @@
 </t>
   </si>
   <si>
-    <t>未使用</t>
+    <t>診断レポートのもとになった検体に関する情報  
+【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>検査結果名称のコードを見れば検体情報が十分に判明するような場合には、この検体情報は冗長になる。複数の検体が関与する場合には、検査や検査グループごとに検体情報が記述されることがある。</t>
@@ -1101,7 +1111,8 @@
 </t>
   </si>
   <si>
-    <t>検査結果</t>
+    <t>診断レポートの一部となるObservationsに関する情報  
+【JP Core仕様】検査結果</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1123,7 +1134,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートに関連づけられた画像検査の詳細情報への参照</t>
+    <t>診断レポートに関連づけれられたDICOM検査画像に関する情報</t>
   </si>
   <si>
     <t>診断的精査中に実施された画像検査の詳細情報へのひとつ/複数のリンク。通常は、DICOM対応のモダリティーによって実施される画像検査だが、必須ではない。完全対応のPACSビューワはこの情報を使用して原画像の一覧を提供できる。</t>
@@ -1143,7 +1154,8 @@
 </t>
   </si>
   <si>
-    <t>このレポートに関連づけられたキー画像</t>
+    <t>診断レポートに関連づけられたメディアに関する情報  
+【JP Core仕様】このレポートに関連づけられたキー画像</t>
   </si>
   <si>
     <t>通常は画像。診断プロセス中に作成され、患者から直接取得されたもの、あるいは調製された検体標本（つまり、関心のあるスライド）のこともある。</t>
@@ -1204,6 +1216,12 @@
 </t>
   </si>
   <si>
+    <t>画像ソースへの参照 / Reference to the image source</t>
+  </si>
+  <si>
+    <t>画像ソースへの参照。 / Reference to the image source.</t>
+  </si>
+  <si>
     <t>例：口腔内写真、jpgで保存されている画像、3Dデータなど</t>
   </si>
   <si>
@@ -1217,6 +1235,10 @@
 </t>
   </si>
   <si>
+    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション）  
+【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
+  </si>
+  <si>
     <t>基本的な結果データの中で失われない結論を提供できる必要があります。 / Need to be able to provide a conclusion that is not lost among the basic result data.</t>
   </si>
   <si>
@@ -1227,6 +1249,10 @@
   </si>
   <si>
     <t>DiagnosticReport.conclusionCode</t>
+  </si>
+  <si>
+    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  
+【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
@@ -1248,7 +1274,7 @@
 </t>
   </si>
   <si>
-    <t>発行されたレポート全体</t>
+    <t>診断サービス/担当者によって発行された診断レポート全体のコンテンツ（例えばPDFファイルなど）</t>
   </si>
   <si>
     <t>複数のフォーマットが許可されるが、それらは意味的に同等である必要がある。「application / pdf」がこのコンテキストで最も信頼でき相互運用可能なものとして推奨される。</t>
@@ -7601,9 +7627,11 @@
         <v>377</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>378</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>81</v>
@@ -7673,7 +7701,7 @@
         <v>81</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>81</v>
@@ -7681,14 +7709,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7710,14 +7738,14 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>383</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>81</v>
@@ -7766,7 +7794,7 @@
         <v>81</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -7784,10 +7812,10 @@
         <v>81</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>81</v>
@@ -7795,10 +7823,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7824,13 +7852,13 @@
         <v>179</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>338</v>
+        <v>388</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7859,28 +7887,28 @@
         <v>182</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="Z55" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -7898,10 +7926,10 @@
         <v>81</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>81</v>
@@ -7909,10 +7937,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7935,19 +7963,19 @@
         <v>81</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>81</v>
@@ -7996,7 +8024,7 @@
         <v>81</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8014,10 +8042,10 @@
         <v>81</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>81</v>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
+++ b/jpcore-r4/release/v1.2.0/StructureDefinition-jp-diagnosticreport-dentaloral.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24</t>
+    <t>2025-07-04</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -489,8 +489,7 @@
 </t>
   </si>
   <si>
-    <t>レポートを識別するビジネス識別子  
-【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
+    <t>レポートを識別するビジネス識別子 【JP Core仕様】当該検査項目に対して、施設内で割り振られる一位の識別子があればそちらを使用する。</t>
   </si>
   <si>
     <t>例：電子カルテ等のオーダ番号、レポート番号、実施日に連番を付加した番号など</t>
@@ -522,8 +521,7 @@
 </t>
   </si>
   <si>
-    <t>元になった検査や診断の依頼  
-【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
+    <t>元になった検査や診断の依頼  【JP Core仕様】オーダ発生元のServiceRequestまたはCarePlanへの参照</t>
   </si>
   <si>
     <t>通常、１結果ごとに１つの検査依頼があるが、状況によっては、複数の検査要求に対して１レポートがある場合がある。また１つの検査依頼に対して複数のレポートが作成される場合もあることに注意。</t>
@@ -544,8 +542,7 @@
     <t>DiagnosticReport.status</t>
   </si>
   <si>
-    <t>診断レポートのステータス  
-【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
+    <t>診断レポートのステータス  【JP Core仕様】レポートの記載状況をバインディングされたコードセットから必ず一つ選ぶ。</t>
   </si>
   <si>
     <t>診断サービスは、暫定/不完全なレポートを日常的に発行し、以前にリリースされたレポートを撤回することもあります。 / Diagnostic services routinely issue provisional/incomplete reports, and sometimes withdraw previously released reports.</t>
@@ -912,8 +909,7 @@
 </t>
   </si>
   <si>
-    <t>レポートの対象、常にではないが、通常は患者  
-【JP Core仕様】Patientリソースを参照</t>
+    <t>レポートの対象、常にではないが、通常は患者  【JP Core仕様】Patientリソースを参照</t>
   </si>
   <si>
     <t>レポートの対象、通常、Patientリソースへの参照。ただし、他のさまざまなソースから収集された検体を対象とすることもある。参照は内容に辿り着ける（解決できる）必要がある（アクセス制御、一時的な使用不可などを考慮に入れる）。解決は、URLから取得するか、リソースタイプによって該当する場合は、絶対参照を正規URLとして扱い、ローカルレジストリ/リポジトリで検索することによって行うことができる。</t>
@@ -945,8 +941,7 @@
 </t>
   </si>
   <si>
-    <t>依頼時におけるヘルスケアイベント（受診など）  
-【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
+    <t>依頼時におけるヘルスケアイベント（受診など） 【JP Core仕様】このレポートを書く切っ掛けとなるEncounterリソースを参照</t>
   </si>
   <si>
     <t>例：診療、歯科健診（検診）、身元不明者調査 ※JP Coreに網羅されていない</t>
@@ -978,8 +973,7 @@
 </t>
   </si>
   <si>
-    <t>臨床的に関連する時刻または時間  
-【JP Core仕様】レポート作成日時</t>
+    <t>臨床的に関連する時刻または時間  【JP Core仕様】レポート作成日時</t>
   </si>
   <si>
     <t>観測値が関連する時間または期間。レポートの対象が患者である場合、これは通常、読影開始の時間であり、日付／時刻自体のみ提供される。実施日時。</t>
@@ -1011,8 +1005,7 @@
 </t>
   </si>
   <si>
-    <t>このバージョンが作成された日時  
-【JP Core仕様】最新のレポート確定日時</t>
+    <t>このバージョンが作成された日時  【JP Core仕様】最新のレポート確定日時</t>
   </si>
   <si>
     <t>通常、レポートがレビューおよび検証・確定された後となる。リソース自体の更新時刻とは異なる場合がある。これは、レポートの実際の提供時刻ではなく、リソース自体の更新時刻はレコード（場合によってはセカンダリコピー）のステータスの更新時刻となるため。</t>
@@ -1041,8 +1034,7 @@
 </t>
   </si>
   <si>
-    <t>レポート内容に責任をもつ診断的サービス  
-【JP Core仕様】レポート確定者</t>
+    <t>レポート内容に責任をもつ診断的サービス  【JP Core仕様】レポート確定者</t>
   </si>
   <si>
     <t>例：歯科医師など</t>
@@ -1070,8 +1062,7 @@
 Reported by</t>
   </si>
   <si>
-    <t>結果の一次解釈者  
-【JP Core仕様】レポートの作成者</t>
+    <t>結果の一次解釈者  【JP Core仕様】レポートの作成者</t>
   </si>
   <si>
     <t>例：歯科医師、歯科研修医など</t>
@@ -1087,8 +1078,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートのもとになった検体に関する情報  
-【JP Core仕様】未使用</t>
+    <t>診断レポートのもとになった検体に関する情報  【JP Core仕様】未使用</t>
   </si>
   <si>
     <t>検査結果名称のコードを見れば検体情報が十分に判明するような場合には、この検体情報は冗長になる。複数の検体が関与する場合には、検査や検査グループごとに検体情報が記述されることがある。</t>
@@ -1111,8 +1101,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートの一部となるObservationsに関する情報  
-【JP Core仕様】検査結果</t>
+    <t>診断レポートの一部となるObservationsに関する情報  【JP Core仕様】検査結果</t>
   </si>
   <si>
     <t>Observationsは階層構造を持てる。</t>
@@ -1154,8 +1143,7 @@
 </t>
   </si>
   <si>
-    <t>診断レポートに関連づけられたメディアに関する情報  
-【JP Core仕様】このレポートに関連づけられたキー画像</t>
+    <t>診断レポートに関連づけられたメディアに関する情報  【JP Core仕様】このレポートに関連づけられたキー画像</t>
   </si>
   <si>
     <t>通常は画像。診断プロセス中に作成され、患者から直接取得されたもの、あるいは調製された検体標本（つまり、関心のあるスライド）のこともある。</t>
@@ -1235,8 +1223,7 @@
 </t>
   </si>
   <si>
-    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション）  
-【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
+    <t>簡潔かつ臨床的な文脈で表現した診断レポートの要約結論（解釈、インプレッション） 【JP Core仕様】原則、未使用。レセプト傷病名などテキスト型で記載も可能。</t>
   </si>
   <si>
     <t>基本的な結果データの中で失われない結論を提供できる必要があります。 / Need to be able to provide a conclusion that is not lost among the basic result data.</t>
@@ -1251,8 +1238,7 @@
     <t>DiagnosticReport.conclusionCode</t>
   </si>
   <si>
-    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  
-【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
+    <t>診断レポートの要約結論（解釈、インプレッション）を表すコード  【JP Core仕様】原則、未使用。レセプト傷病名などのCodeableConcept型で定義も可能。</t>
   </si>
   <si>
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、独自の構造を提供する必要がある。</t>
